--- a/infra_auto_diag/보고서_양식_Linux.xlsx
+++ b/infra_auto_diag/보고서_양식_Linux.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'0. 표지'!$A$1:$L$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'1. 진단 대상'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2-1. 요약결과(그래프)'!$A$1:$X$102</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2-1. 요약결과(그래프)'!$A$1:$X$104</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'3-1. 진단 결과(Linux)'!$E$6:$M$74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'2-2. 요약 진단결과(Linux)'!$2:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'3-1. 진단 결과(Linux)'!$B:$D,'3-1. 진단 결과(Linux)'!$2:$5</definedName>

--- a/infra_auto_diag/보고서_양식_Linux.xlsx
+++ b/infra_auto_diag/보고서_양식_Linux.xlsx
@@ -2474,7 +2474,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="404">
+  <cellXfs count="423">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3628,6 +3628,63 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="77" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="78" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -7372,7 +7429,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2-1. 요약결과(그래프)'!$C$72:$C$76</c:f>
+              <c:f>'2-1. 요약결과(그래프)'!$BA$72:$BA$76</c:f>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -7406,7 +7463,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'2-1. 요약결과(그래프)'!$D$72:$D$76</c:f>
+              <c:f>'2-1. 요약결과(그래프)'!$BB$72:$BB$76</c:f>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -11896,7 +11953,7 @@
     </row>
     <row r="72" spans="1:44" ht="15" customHeight="1">
       <c r="A72" s="179"/>
-      <c r="B72" s="233">
+      <c r="B72" s="421">
         <f>SUBSTITUTE('2-2. 요약 진단결과(Linux)'!B6,CHAR(10),"")</f>
       </c>
       <c r="C72" s="211">
@@ -11945,10 +12002,16 @@
       <c r="AP72" s="179"/>
       <c r="AQ72" s="179"/>
       <c r="AR72" s="179"/>
+      <c r="BA72" s="211">
+        <f>IF(ISNUMBER(C72),C72,NA())</f>
+      </c>
+      <c r="BB72" s="234">
+        <f>IF(ISNUMBER(D72),D72,NA())</f>
+      </c>
     </row>
     <row r="73" spans="1:44" ht="15" customHeight="1">
       <c r="A73" s="179"/>
-      <c r="B73" s="233">
+      <c r="B73" s="421">
         <f>SUBSTITUTE('2-2. 요약 진단결과(Linux)'!B19,CHAR(10),"")</f>
       </c>
       <c r="C73" s="211">
@@ -11997,10 +12060,16 @@
       <c r="AP73" s="179"/>
       <c r="AQ73" s="179"/>
       <c r="AR73" s="179"/>
+      <c r="BA73" s="211">
+        <f>IF(ISNUMBER(C73),C73,NA())</f>
+      </c>
+      <c r="BB73" s="234">
+        <f>IF(ISNUMBER(D73),D73,NA())</f>
+      </c>
     </row>
     <row r="74" spans="1:44" ht="15" customHeight="1">
       <c r="A74" s="179"/>
-      <c r="B74" s="233">
+      <c r="B74" s="421">
         <f>SUBSTITUTE('2-2. 요약 진단결과(Linux)'!B39,CHAR(10),"")</f>
       </c>
       <c r="C74" s="211">
@@ -12049,10 +12118,16 @@
       <c r="AP74" s="179"/>
       <c r="AQ74" s="179"/>
       <c r="AR74" s="179"/>
+      <c r="BA74" s="211">
+        <f>IF(ISNUMBER(C74),C74,NA())</f>
+      </c>
+      <c r="BB74" s="234">
+        <f>IF(ISNUMBER(D74),D74,NA())</f>
+      </c>
     </row>
     <row r="75" spans="1:44" ht="15" customHeight="1">
       <c r="A75" s="179"/>
-      <c r="B75" s="233">
+      <c r="B75" s="421">
         <f>SUBSTITUTE('2-2. 요약 진단결과(Linux)'!B69,CHAR(10),"")</f>
       </c>
       <c r="C75" s="211">
@@ -12101,10 +12176,16 @@
       <c r="AP75" s="179"/>
       <c r="AQ75" s="179"/>
       <c r="AR75" s="179"/>
+      <c r="BA75" s="211">
+        <f>IF(ISNUMBER(C75),C75,NA())</f>
+      </c>
+      <c r="BB75" s="234">
+        <f>IF(ISNUMBER(D75),D75,NA())</f>
+      </c>
     </row>
     <row r="76" spans="1:44" ht="15" customHeight="1" thickBot="1">
       <c r="A76" s="179"/>
-      <c r="B76" s="235">
+      <c r="B76" s="422">
         <f>SUBSTITUTE('2-2. 요약 진단결과(Linux)'!B70,CHAR(10),"")</f>
       </c>
       <c r="C76" s="236">
@@ -12153,6 +12234,12 @@
       <c r="AP76" s="179"/>
       <c r="AQ76" s="179"/>
       <c r="AR76" s="179"/>
+      <c r="BA76" s="236">
+        <f>IF(ISNUMBER(C76),C76,NA())</f>
+      </c>
+      <c r="BB76" s="237">
+        <f>IF(ISNUMBER(D76),D76,NA())</f>
+      </c>
     </row>
     <row r="77" spans="1:44" ht="6.9" customHeight="1">
       <c r="A77" s="179"/>
@@ -54889,16 +54976,16 @@
       <c r="E6" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="404">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A4),FALSE)),"")</f>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="404">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A4),FALSE)),"")</f>
       </c>
-      <c r="H6" s="58">
+      <c r="H6" s="404">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A4),FALSE)),"")</f>
       </c>
-      <c r="I6" s="223">
+      <c r="I6" s="405">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A4),FALSE)),"")</f>
       </c>
       <c r="J6" s="14"/>
@@ -54940,16 +55027,16 @@
       <c r="E7" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A5),FALSE)),"")</f>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A5),FALSE)),"")</f>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A5),FALSE)),"")</f>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A5),FALSE)),"")</f>
       </c>
       <c r="J7" s="14"/>
@@ -54989,16 +55076,16 @@
       <c r="E8" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A6),FALSE)),"")</f>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A6),FALSE)),"")</f>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A6),FALSE)),"")</f>
       </c>
-      <c r="I8" s="68">
+      <c r="I8" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A6),FALSE)),"")</f>
       </c>
       <c r="J8" s="14"/>
@@ -55038,16 +55125,16 @@
       <c r="E9" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A7),FALSE)),"")</f>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A7),FALSE)),"")</f>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A7),FALSE)),"")</f>
       </c>
-      <c r="I9" s="68">
+      <c r="I9" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A7),FALSE)),"")</f>
       </c>
       <c r="J9" s="14"/>
@@ -55087,16 +55174,16 @@
       <c r="E10" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A8),FALSE)),"")</f>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A8),FALSE)),"")</f>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A8),FALSE)),"")</f>
       </c>
-      <c r="I10" s="68">
+      <c r="I10" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A8),FALSE)),"")</f>
       </c>
       <c r="J10" s="14"/>
@@ -55136,16 +55223,16 @@
       <c r="E11" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A9),FALSE)),"")</f>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A9),FALSE)),"")</f>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A9),FALSE)),"")</f>
       </c>
-      <c r="I11" s="68">
+      <c r="I11" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A9),FALSE)),"")</f>
       </c>
       <c r="J11" s="14"/>
@@ -55185,16 +55272,16 @@
       <c r="E12" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A10),FALSE)),"")</f>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A10),FALSE)),"")</f>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A10),FALSE)),"")</f>
       </c>
-      <c r="I12" s="68">
+      <c r="I12" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A10),FALSE)),"")</f>
       </c>
       <c r="J12" s="14"/>
@@ -55234,16 +55321,16 @@
       <c r="E13" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A11),FALSE)),"")</f>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A11),FALSE)),"")</f>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A11),FALSE)),"")</f>
       </c>
-      <c r="I13" s="68">
+      <c r="I13" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A11),FALSE)),"")</f>
       </c>
       <c r="J13" s="14"/>
@@ -55283,16 +55370,16 @@
       <c r="E14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="62">
+      <c r="F14" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A12),FALSE)),"")</f>
       </c>
-      <c r="G14" s="62">
+      <c r="G14" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A12),FALSE)),"")</f>
       </c>
-      <c r="H14" s="62">
+      <c r="H14" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A12),FALSE)),"")</f>
       </c>
-      <c r="I14" s="66">
+      <c r="I14" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A12),FALSE)),"")</f>
       </c>
       <c r="J14" s="14"/>
@@ -55332,16 +55419,16 @@
       <c r="E15" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A13),FALSE)),"")</f>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A13),FALSE)),"")</f>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A13),FALSE)),"")</f>
       </c>
-      <c r="I15" s="68">
+      <c r="I15" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A13),FALSE)),"")</f>
       </c>
       <c r="J15" s="14"/>
@@ -55381,16 +55468,16 @@
       <c r="E16" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A14),FALSE)),"")</f>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A14),FALSE)),"")</f>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A14),FALSE)),"")</f>
       </c>
-      <c r="I16" s="68">
+      <c r="I16" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A14),FALSE)),"")</f>
       </c>
       <c r="J16" s="14"/>
@@ -55430,16 +55517,16 @@
       <c r="E17" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A15),FALSE)),"")</f>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A15),FALSE)),"")</f>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A15),FALSE)),"")</f>
       </c>
-      <c r="I17" s="68">
+      <c r="I17" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A15),FALSE)),"")</f>
       </c>
       <c r="J17" s="14"/>
@@ -55479,16 +55566,16 @@
       <c r="E18" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="410">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A16),FALSE)),"")</f>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="410">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A16),FALSE)),"")</f>
       </c>
-      <c r="H18" s="61">
+      <c r="H18" s="410">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A16),FALSE)),"")</f>
       </c>
-      <c r="I18" s="67">
+      <c r="I18" s="411">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A16),FALSE)),"")</f>
       </c>
       <c r="J18" s="14"/>
@@ -55530,16 +55617,16 @@
       <c r="E19" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="83">
+      <c r="F19" s="412">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A17),FALSE)),"")</f>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="412">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A17),FALSE)),"")</f>
       </c>
-      <c r="H19" s="83">
+      <c r="H19" s="412">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A17),FALSE)),"")</f>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="413">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A17),FALSE)),"")</f>
       </c>
       <c r="J19" s="14"/>
@@ -55581,16 +55668,16 @@
       <c r="E20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F20" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A18),FALSE)),"")</f>
       </c>
-      <c r="G20" s="62">
+      <c r="G20" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A18),FALSE)),"")</f>
       </c>
-      <c r="H20" s="62">
+      <c r="H20" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A18),FALSE)),"")</f>
       </c>
-      <c r="I20" s="66">
+      <c r="I20" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A18),FALSE)),"")</f>
       </c>
       <c r="J20" s="14"/>
@@ -55630,16 +55717,16 @@
       <c r="E21" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="62">
+      <c r="F21" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A19),FALSE)),"")</f>
       </c>
-      <c r="G21" s="62">
+      <c r="G21" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A19),FALSE)),"")</f>
       </c>
-      <c r="H21" s="62">
+      <c r="H21" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A19),FALSE)),"")</f>
       </c>
-      <c r="I21" s="66">
+      <c r="I21" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A19),FALSE)),"")</f>
       </c>
       <c r="J21" s="14"/>
@@ -55679,16 +55766,16 @@
       <c r="E22" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F22" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A20),FALSE)),"")</f>
       </c>
-      <c r="G22" s="62">
+      <c r="G22" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A20),FALSE)),"")</f>
       </c>
-      <c r="H22" s="62">
+      <c r="H22" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A20),FALSE)),"")</f>
       </c>
-      <c r="I22" s="66">
+      <c r="I22" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A20),FALSE)),"")</f>
       </c>
       <c r="J22" s="14"/>
@@ -55728,16 +55815,16 @@
       <c r="E23" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A21),FALSE)),"")</f>
       </c>
-      <c r="G23" s="62">
+      <c r="G23" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A21),FALSE)),"")</f>
       </c>
-      <c r="H23" s="62">
+      <c r="H23" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A21),FALSE)),"")</f>
       </c>
-      <c r="I23" s="66">
+      <c r="I23" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A21),FALSE)),"")</f>
       </c>
       <c r="J23" s="14"/>
@@ -55777,16 +55864,16 @@
       <c r="E24" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="62">
+      <c r="F24" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A22),FALSE)),"")</f>
       </c>
-      <c r="G24" s="62">
+      <c r="G24" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A22),FALSE)),"")</f>
       </c>
-      <c r="H24" s="62">
+      <c r="H24" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A22),FALSE)),"")</f>
       </c>
-      <c r="I24" s="66">
+      <c r="I24" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A22),FALSE)),"")</f>
       </c>
       <c r="J24" s="14"/>
@@ -55826,16 +55913,16 @@
       <c r="E25" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="62">
+      <c r="F25" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A23),FALSE)),"")</f>
       </c>
-      <c r="G25" s="62">
+      <c r="G25" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A23),FALSE)),"")</f>
       </c>
-      <c r="H25" s="62">
+      <c r="H25" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A23),FALSE)),"")</f>
       </c>
-      <c r="I25" s="66">
+      <c r="I25" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A23),FALSE)),"")</f>
       </c>
       <c r="J25" s="14"/>
@@ -55875,16 +55962,16 @@
       <c r="E26" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="62">
+      <c r="F26" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A24),FALSE)),"")</f>
       </c>
-      <c r="G26" s="62">
+      <c r="G26" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A24),FALSE)),"")</f>
       </c>
-      <c r="H26" s="62">
+      <c r="H26" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A24),FALSE)),"")</f>
       </c>
-      <c r="I26" s="66">
+      <c r="I26" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A24),FALSE)),"")</f>
       </c>
       <c r="J26" s="14"/>
@@ -55924,16 +56011,16 @@
       <c r="E27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="62">
+      <c r="F27" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A25),FALSE)),"")</f>
       </c>
-      <c r="G27" s="62">
+      <c r="G27" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A25),FALSE)),"")</f>
       </c>
-      <c r="H27" s="62">
+      <c r="H27" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A25),FALSE)),"")</f>
       </c>
-      <c r="I27" s="66">
+      <c r="I27" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A25),FALSE)),"")</f>
       </c>
       <c r="J27" s="14"/>
@@ -55973,16 +56060,16 @@
       <c r="E28" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F28" s="62">
+      <c r="F28" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A26),FALSE)),"")</f>
       </c>
-      <c r="G28" s="62">
+      <c r="G28" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A26),FALSE)),"")</f>
       </c>
-      <c r="H28" s="62">
+      <c r="H28" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A26),FALSE)),"")</f>
       </c>
-      <c r="I28" s="66">
+      <c r="I28" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A26),FALSE)),"")</f>
       </c>
       <c r="J28" s="14"/>
@@ -56022,16 +56109,16 @@
       <c r="E29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A27),FALSE)),"")</f>
       </c>
-      <c r="G29" s="62">
+      <c r="G29" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A27),FALSE)),"")</f>
       </c>
-      <c r="H29" s="62">
+      <c r="H29" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A27),FALSE)),"")</f>
       </c>
-      <c r="I29" s="66">
+      <c r="I29" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A27),FALSE)),"")</f>
       </c>
       <c r="J29" s="14"/>
@@ -56071,16 +56158,16 @@
       <c r="E30" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F30" s="62">
+      <c r="F30" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A28),FALSE)),"")</f>
       </c>
-      <c r="G30" s="62">
+      <c r="G30" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A28),FALSE)),"")</f>
       </c>
-      <c r="H30" s="62">
+      <c r="H30" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A28),FALSE)),"")</f>
       </c>
-      <c r="I30" s="66">
+      <c r="I30" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A28),FALSE)),"")</f>
       </c>
       <c r="J30" s="14"/>
@@ -56120,16 +56207,16 @@
       <c r="E31" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F31" s="62">
+      <c r="F31" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A29),FALSE)),"")</f>
       </c>
-      <c r="G31" s="62">
+      <c r="G31" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A29),FALSE)),"")</f>
       </c>
-      <c r="H31" s="62">
+      <c r="H31" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A29),FALSE)),"")</f>
       </c>
-      <c r="I31" s="66">
+      <c r="I31" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A29),FALSE)),"")</f>
       </c>
       <c r="J31" s="14"/>
@@ -56169,16 +56256,16 @@
       <c r="E32" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="62">
+      <c r="F32" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A30),FALSE)),"")</f>
       </c>
-      <c r="G32" s="62">
+      <c r="G32" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A30),FALSE)),"")</f>
       </c>
-      <c r="H32" s="62">
+      <c r="H32" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A30),FALSE)),"")</f>
       </c>
-      <c r="I32" s="66">
+      <c r="I32" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A30),FALSE)),"")</f>
       </c>
       <c r="J32" s="14"/>
@@ -56218,16 +56305,16 @@
       <c r="E33" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="62">
+      <c r="F33" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A31),FALSE)),"")</f>
       </c>
-      <c r="G33" s="62">
+      <c r="G33" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A31),FALSE)),"")</f>
       </c>
-      <c r="H33" s="62">
+      <c r="H33" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A31),FALSE)),"")</f>
       </c>
-      <c r="I33" s="66">
+      <c r="I33" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A31),FALSE)),"")</f>
       </c>
       <c r="J33" s="14"/>
@@ -56267,16 +56354,16 @@
       <c r="E34" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F34" s="62">
+      <c r="F34" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A32),FALSE)),"")</f>
       </c>
-      <c r="G34" s="62">
+      <c r="G34" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A32),FALSE)),"")</f>
       </c>
-      <c r="H34" s="62">
+      <c r="H34" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A32),FALSE)),"")</f>
       </c>
-      <c r="I34" s="66">
+      <c r="I34" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A32),FALSE)),"")</f>
       </c>
       <c r="J34" s="14"/>
@@ -56316,16 +56403,16 @@
       <c r="E35" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F35" s="62">
+      <c r="F35" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A33),FALSE)),"")</f>
       </c>
-      <c r="G35" s="62">
+      <c r="G35" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A33),FALSE)),"")</f>
       </c>
-      <c r="H35" s="62">
+      <c r="H35" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A33),FALSE)),"")</f>
       </c>
-      <c r="I35" s="66">
+      <c r="I35" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A33),FALSE)),"")</f>
       </c>
       <c r="J35" s="14"/>
@@ -56365,16 +56452,16 @@
       <c r="E36" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="62">
+      <c r="F36" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A34),FALSE)),"")</f>
       </c>
-      <c r="G36" s="62">
+      <c r="G36" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A34),FALSE)),"")</f>
       </c>
-      <c r="H36" s="62">
+      <c r="H36" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A34),FALSE)),"")</f>
       </c>
-      <c r="I36" s="66">
+      <c r="I36" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A34),FALSE)),"")</f>
       </c>
       <c r="J36" s="14"/>
@@ -56414,16 +56501,16 @@
       <c r="E37" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F37" s="62">
+      <c r="F37" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A35),FALSE)),"")</f>
       </c>
-      <c r="G37" s="62">
+      <c r="G37" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A35),FALSE)),"")</f>
       </c>
-      <c r="H37" s="62">
+      <c r="H37" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A35),FALSE)),"")</f>
       </c>
-      <c r="I37" s="66">
+      <c r="I37" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A35),FALSE)),"")</f>
       </c>
       <c r="J37" s="14"/>
@@ -56463,16 +56550,16 @@
       <c r="E38" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="F38" s="61">
+      <c r="F38" s="410">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A36),FALSE)),"")</f>
       </c>
-      <c r="G38" s="61">
+      <c r="G38" s="410">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A36),FALSE)),"")</f>
       </c>
-      <c r="H38" s="61">
+      <c r="H38" s="410">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A36),FALSE)),"")</f>
       </c>
-      <c r="I38" s="67">
+      <c r="I38" s="411">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A36),FALSE)),"")</f>
       </c>
       <c r="J38" s="14"/>
@@ -56514,16 +56601,16 @@
       <c r="E39" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A37),FALSE)),"")</f>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A37),FALSE)),"")</f>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A37),FALSE)),"")</f>
       </c>
-      <c r="I39" s="68">
+      <c r="I39" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A37),FALSE)),"")</f>
       </c>
       <c r="J39" s="14"/>
@@ -56565,16 +56652,16 @@
       <c r="E40" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A38),FALSE)),"")</f>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A38),FALSE)),"")</f>
       </c>
-      <c r="H40" s="20">
+      <c r="H40" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A38),FALSE)),"")</f>
       </c>
-      <c r="I40" s="68">
+      <c r="I40" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A38),FALSE)),"")</f>
       </c>
       <c r="J40" s="14"/>
@@ -56614,16 +56701,16 @@
       <c r="E41" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A39),FALSE)),"")</f>
       </c>
-      <c r="G41" s="20">
+      <c r="G41" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A39),FALSE)),"")</f>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A39),FALSE)),"")</f>
       </c>
-      <c r="I41" s="68">
+      <c r="I41" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A39),FALSE)),"")</f>
       </c>
       <c r="J41" s="14"/>
@@ -56663,16 +56750,16 @@
       <c r="E42" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="62">
+      <c r="F42" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A40),FALSE)),"")</f>
       </c>
-      <c r="G42" s="62">
+      <c r="G42" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A40),FALSE)),"")</f>
       </c>
-      <c r="H42" s="62">
+      <c r="H42" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A40),FALSE)),"")</f>
       </c>
-      <c r="I42" s="66">
+      <c r="I42" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A40),FALSE)),"")</f>
       </c>
       <c r="J42" s="14"/>
@@ -56712,16 +56799,16 @@
       <c r="E43" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A41),FALSE)),"")</f>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A41),FALSE)),"")</f>
       </c>
-      <c r="H43" s="20">
+      <c r="H43" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A41),FALSE)),"")</f>
       </c>
-      <c r="I43" s="68">
+      <c r="I43" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A41),FALSE)),"")</f>
       </c>
       <c r="J43" s="14"/>
@@ -56761,16 +56848,16 @@
       <c r="E44" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="62">
+      <c r="F44" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A42),FALSE)),"")</f>
       </c>
-      <c r="G44" s="62">
+      <c r="G44" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A42),FALSE)),"")</f>
       </c>
-      <c r="H44" s="62">
+      <c r="H44" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A42),FALSE)),"")</f>
       </c>
-      <c r="I44" s="66">
+      <c r="I44" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A42),FALSE)),"")</f>
       </c>
       <c r="J44" s="14"/>
@@ -56810,16 +56897,16 @@
       <c r="E45" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A43),FALSE)),"")</f>
       </c>
-      <c r="G45" s="20">
+      <c r="G45" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A43),FALSE)),"")</f>
       </c>
-      <c r="H45" s="20">
+      <c r="H45" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A43),FALSE)),"")</f>
       </c>
-      <c r="I45" s="68">
+      <c r="I45" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A43),FALSE)),"")</f>
       </c>
       <c r="J45" s="14"/>
@@ -56859,16 +56946,16 @@
       <c r="E46" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A44),FALSE)),"")</f>
       </c>
-      <c r="G46" s="20">
+      <c r="G46" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A44),FALSE)),"")</f>
       </c>
-      <c r="H46" s="20">
+      <c r="H46" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A44),FALSE)),"")</f>
       </c>
-      <c r="I46" s="68">
+      <c r="I46" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A44),FALSE)),"")</f>
       </c>
       <c r="J46" s="14"/>
@@ -56908,16 +56995,16 @@
       <c r="E47" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A45),FALSE)),"")</f>
       </c>
-      <c r="G47" s="20">
+      <c r="G47" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A45),FALSE)),"")</f>
       </c>
-      <c r="H47" s="20">
+      <c r="H47" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A45),FALSE)),"")</f>
       </c>
-      <c r="I47" s="68">
+      <c r="I47" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A45),FALSE)),"")</f>
       </c>
       <c r="J47" s="14"/>
@@ -56957,16 +57044,16 @@
       <c r="E48" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A46),FALSE)),"")</f>
       </c>
-      <c r="G48" s="20">
+      <c r="G48" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A46),FALSE)),"")</f>
       </c>
-      <c r="H48" s="20">
+      <c r="H48" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A46),FALSE)),"")</f>
       </c>
-      <c r="I48" s="68">
+      <c r="I48" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A46),FALSE)),"")</f>
       </c>
       <c r="J48" s="14"/>
@@ -57006,16 +57093,16 @@
       <c r="E49" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A47),FALSE)),"")</f>
       </c>
-      <c r="G49" s="20">
+      <c r="G49" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A47),FALSE)),"")</f>
       </c>
-      <c r="H49" s="20">
+      <c r="H49" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A47),FALSE)),"")</f>
       </c>
-      <c r="I49" s="68">
+      <c r="I49" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A47),FALSE)),"")</f>
       </c>
       <c r="J49" s="14"/>
@@ -57055,16 +57142,16 @@
       <c r="E50" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="63">
+      <c r="F50" s="414">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A48),FALSE)),"")</f>
       </c>
-      <c r="G50" s="63">
+      <c r="G50" s="414">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A48),FALSE)),"")</f>
       </c>
-      <c r="H50" s="63">
+      <c r="H50" s="414">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A48),FALSE)),"")</f>
       </c>
-      <c r="I50" s="225">
+      <c r="I50" s="415">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A48),FALSE)),"")</f>
       </c>
       <c r="J50" s="14"/>
@@ -57104,16 +57191,16 @@
       <c r="E51" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F51" s="62">
+      <c r="F51" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A49),FALSE)),"")</f>
       </c>
-      <c r="G51" s="62">
+      <c r="G51" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A49),FALSE)),"")</f>
       </c>
-      <c r="H51" s="62">
+      <c r="H51" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A49),FALSE)),"")</f>
       </c>
-      <c r="I51" s="66">
+      <c r="I51" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A49),FALSE)),"")</f>
       </c>
       <c r="J51" s="14"/>
@@ -57153,16 +57240,16 @@
       <c r="E52" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F52" s="62">
+      <c r="F52" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A50),FALSE)),"")</f>
       </c>
-      <c r="G52" s="62">
+      <c r="G52" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A50),FALSE)),"")</f>
       </c>
-      <c r="H52" s="62">
+      <c r="H52" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A50),FALSE)),"")</f>
       </c>
-      <c r="I52" s="66">
+      <c r="I52" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A50),FALSE)),"")</f>
       </c>
       <c r="J52" s="14"/>
@@ -57202,16 +57289,16 @@
       <c r="E53" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F53" s="62">
+      <c r="F53" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A51),FALSE)),"")</f>
       </c>
-      <c r="G53" s="62">
+      <c r="G53" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A51),FALSE)),"")</f>
       </c>
-      <c r="H53" s="62">
+      <c r="H53" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A51),FALSE)),"")</f>
       </c>
-      <c r="I53" s="66">
+      <c r="I53" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A51),FALSE)),"")</f>
       </c>
       <c r="J53" s="14"/>
@@ -57251,16 +57338,16 @@
       <c r="E54" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F54" s="62">
+      <c r="F54" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A52),FALSE)),"")</f>
       </c>
-      <c r="G54" s="62">
+      <c r="G54" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A52),FALSE)),"")</f>
       </c>
-      <c r="H54" s="62">
+      <c r="H54" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A52),FALSE)),"")</f>
       </c>
-      <c r="I54" s="66">
+      <c r="I54" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A52),FALSE)),"")</f>
       </c>
       <c r="J54" s="14"/>
@@ -57300,16 +57387,16 @@
       <c r="E55" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F55" s="62">
+      <c r="F55" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A53),FALSE)),"")</f>
       </c>
-      <c r="G55" s="62">
+      <c r="G55" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A53),FALSE)),"")</f>
       </c>
-      <c r="H55" s="62">
+      <c r="H55" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A53),FALSE)),"")</f>
       </c>
-      <c r="I55" s="66">
+      <c r="I55" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A53),FALSE)),"")</f>
       </c>
       <c r="J55" s="14"/>
@@ -57349,16 +57436,16 @@
       <c r="E56" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F56" s="62">
+      <c r="F56" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A54),FALSE)),"")</f>
       </c>
-      <c r="G56" s="62">
+      <c r="G56" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A54),FALSE)),"")</f>
       </c>
-      <c r="H56" s="62">
+      <c r="H56" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A54),FALSE)),"")</f>
       </c>
-      <c r="I56" s="66">
+      <c r="I56" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A54),FALSE)),"")</f>
       </c>
       <c r="J56" s="14"/>
@@ -57398,16 +57485,16 @@
       <c r="E57" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F57" s="62">
+      <c r="F57" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A55),FALSE)),"")</f>
       </c>
-      <c r="G57" s="62">
+      <c r="G57" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A55),FALSE)),"")</f>
       </c>
-      <c r="H57" s="62">
+      <c r="H57" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A55),FALSE)),"")</f>
       </c>
-      <c r="I57" s="66">
+      <c r="I57" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A55),FALSE)),"")</f>
       </c>
       <c r="J57" s="14"/>
@@ -57447,16 +57534,16 @@
       <c r="E58" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F58" s="62">
+      <c r="F58" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A56),FALSE)),"")</f>
       </c>
-      <c r="G58" s="62">
+      <c r="G58" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A56),FALSE)),"")</f>
       </c>
-      <c r="H58" s="62">
+      <c r="H58" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A56),FALSE)),"")</f>
       </c>
-      <c r="I58" s="66">
+      <c r="I58" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A56),FALSE)),"")</f>
       </c>
       <c r="J58" s="14"/>
@@ -57496,16 +57583,16 @@
       <c r="E59" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F59" s="62">
+      <c r="F59" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A57),FALSE)),"")</f>
       </c>
-      <c r="G59" s="62">
+      <c r="G59" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A57),FALSE)),"")</f>
       </c>
-      <c r="H59" s="62">
+      <c r="H59" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A57),FALSE)),"")</f>
       </c>
-      <c r="I59" s="66">
+      <c r="I59" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A57),FALSE)),"")</f>
       </c>
       <c r="J59" s="14"/>
@@ -57545,16 +57632,16 @@
       <c r="E60" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F60" s="62">
+      <c r="F60" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A58),FALSE)),"")</f>
       </c>
-      <c r="G60" s="62">
+      <c r="G60" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A58),FALSE)),"")</f>
       </c>
-      <c r="H60" s="62">
+      <c r="H60" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A58),FALSE)),"")</f>
       </c>
-      <c r="I60" s="66">
+      <c r="I60" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A58),FALSE)),"")</f>
       </c>
       <c r="J60" s="14"/>
@@ -57594,16 +57681,16 @@
       <c r="E61" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F61" s="62">
+      <c r="F61" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A59),FALSE)),"")</f>
       </c>
-      <c r="G61" s="62">
+      <c r="G61" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A59),FALSE)),"")</f>
       </c>
-      <c r="H61" s="62">
+      <c r="H61" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A59),FALSE)),"")</f>
       </c>
-      <c r="I61" s="66">
+      <c r="I61" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A59),FALSE)),"")</f>
       </c>
       <c r="J61" s="14"/>
@@ -57643,16 +57730,16 @@
       <c r="E62" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F62" s="62">
+      <c r="F62" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A60),FALSE)),"")</f>
       </c>
-      <c r="G62" s="62">
+      <c r="G62" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A60),FALSE)),"")</f>
       </c>
-      <c r="H62" s="62">
+      <c r="H62" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A60),FALSE)),"")</f>
       </c>
-      <c r="I62" s="66">
+      <c r="I62" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A60),FALSE)),"")</f>
       </c>
       <c r="J62" s="14"/>
@@ -57692,16 +57779,16 @@
       <c r="E63" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F63" s="62">
+      <c r="F63" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A61),FALSE)),"")</f>
       </c>
-      <c r="G63" s="62">
+      <c r="G63" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A61),FALSE)),"")</f>
       </c>
-      <c r="H63" s="62">
+      <c r="H63" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A61),FALSE)),"")</f>
       </c>
-      <c r="I63" s="66">
+      <c r="I63" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A61),FALSE)),"")</f>
       </c>
       <c r="J63" s="14"/>
@@ -57741,16 +57828,16 @@
       <c r="E64" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F64" s="62">
+      <c r="F64" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A62),FALSE)),"")</f>
       </c>
-      <c r="G64" s="62">
+      <c r="G64" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A62),FALSE)),"")</f>
       </c>
-      <c r="H64" s="62">
+      <c r="H64" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A62),FALSE)),"")</f>
       </c>
-      <c r="I64" s="66">
+      <c r="I64" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A62),FALSE)),"")</f>
       </c>
       <c r="J64" s="14"/>
@@ -57790,16 +57877,16 @@
       <c r="E65" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F65" s="62">
+      <c r="F65" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A63),FALSE)),"")</f>
       </c>
-      <c r="G65" s="62">
+      <c r="G65" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A63),FALSE)),"")</f>
       </c>
-      <c r="H65" s="62">
+      <c r="H65" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A63),FALSE)),"")</f>
       </c>
-      <c r="I65" s="66">
+      <c r="I65" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A63),FALSE)),"")</f>
       </c>
       <c r="J65" s="14"/>
@@ -57839,16 +57926,16 @@
       <c r="E66" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F66" s="62">
+      <c r="F66" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A64),FALSE)),"")</f>
       </c>
-      <c r="G66" s="62">
+      <c r="G66" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A64),FALSE)),"")</f>
       </c>
-      <c r="H66" s="62">
+      <c r="H66" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A64),FALSE)),"")</f>
       </c>
-      <c r="I66" s="66">
+      <c r="I66" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A64),FALSE)),"")</f>
       </c>
       <c r="J66" s="14"/>
@@ -57888,16 +57975,16 @@
       <c r="E67" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F67" s="62">
+      <c r="F67" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A65),FALSE)),"")</f>
       </c>
-      <c r="G67" s="62">
+      <c r="G67" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A65),FALSE)),"")</f>
       </c>
-      <c r="H67" s="62">
+      <c r="H67" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A65),FALSE)),"")</f>
       </c>
-      <c r="I67" s="66">
+      <c r="I67" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A65),FALSE)),"")</f>
       </c>
       <c r="J67" s="14"/>
@@ -57937,16 +58024,16 @@
       <c r="E68" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="F68" s="61">
+      <c r="F68" s="410">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A66),FALSE)),"")</f>
       </c>
-      <c r="G68" s="61">
+      <c r="G68" s="410">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A66),FALSE)),"")</f>
       </c>
-      <c r="H68" s="61">
+      <c r="H68" s="410">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A66),FALSE)),"")</f>
       </c>
-      <c r="I68" s="67">
+      <c r="I68" s="411">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A66),FALSE)),"")</f>
       </c>
       <c r="J68" s="14"/>
@@ -57988,16 +58075,16 @@
       <c r="E69" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="F69" s="62">
+      <c r="F69" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A67),FALSE)),"")</f>
       </c>
-      <c r="G69" s="62">
+      <c r="G69" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A67),FALSE)),"")</f>
       </c>
-      <c r="H69" s="62">
+      <c r="H69" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A67),FALSE)),"")</f>
       </c>
-      <c r="I69" s="66">
+      <c r="I69" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A67),FALSE)),"")</f>
       </c>
       <c r="J69" s="14"/>
@@ -58041,16 +58128,16 @@
       <c r="E70" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F70" s="20">
+      <c r="F70" s="406">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A68),FALSE)),"")</f>
       </c>
-      <c r="G70" s="20">
+      <c r="G70" s="406">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A68),FALSE)),"")</f>
       </c>
-      <c r="H70" s="20">
+      <c r="H70" s="406">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A68),FALSE)),"")</f>
       </c>
-      <c r="I70" s="68">
+      <c r="I70" s="407">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A68),FALSE)),"")</f>
       </c>
       <c r="J70" s="14"/>
@@ -58092,16 +58179,16 @@
       <c r="E71" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F71" s="62">
+      <c r="F71" s="408">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A69),FALSE)),"")</f>
       </c>
-      <c r="G71" s="62">
+      <c r="G71" s="408">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A69),FALSE)),"")</f>
       </c>
-      <c r="H71" s="62">
+      <c r="H71" s="408">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A69),FALSE)),"")</f>
       </c>
-      <c r="I71" s="66">
+      <c r="I71" s="409">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A69),FALSE)),"")</f>
       </c>
       <c r="J71" s="14"/>
@@ -58141,16 +58228,16 @@
       <c r="E72" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="F72" s="61">
+      <c r="F72" s="410">
         <f>IFERROR(T(HLOOKUP(F$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A70),FALSE)),"")</f>
       </c>
-      <c r="G72" s="61">
+      <c r="G72" s="410">
         <f>IFERROR(T(HLOOKUP(G$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A70),FALSE)),"")</f>
       </c>
-      <c r="H72" s="61">
+      <c r="H72" s="410">
         <f>IFERROR(T(HLOOKUP(H$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A70),FALSE)),"")</f>
       </c>
-      <c r="I72" s="67">
+      <c r="I72" s="411">
         <f>IFERROR(T(HLOOKUP(I$3,'3-1. 진단 결과(Linux)'!$F$3:$M$72,ROW(A70),FALSE)),"")</f>
       </c>
       <c r="J72" s="14"/>
@@ -58188,16 +58275,16 @@
       </c>
       <c r="D73" s="276"/>
       <c r="E73" s="277"/>
-      <c r="F73" s="18">
+      <c r="F73" s="417">
         <f>IF(COUNTIF(F$6:F$72,"?*")=0,"",COUNTIF(F$6:F$72,"취약"))</f>
       </c>
-      <c r="G73" s="18">
+      <c r="G73" s="417">
         <f>IF(COUNTIF(G$6:G$72,"?*")=0,"",COUNTIF(G$6:G$72,"취약"))</f>
       </c>
-      <c r="H73" s="18">
+      <c r="H73" s="417">
         <f>IF(COUNTIF(H$6:H$72,"?*")=0,"",COUNTIF(H$6:H$72,"취약"))</f>
       </c>
-      <c r="I73" s="227">
+      <c r="I73" s="418">
         <f>IF(COUNTIF(I$6:I$72,"?*")=0,"",COUNTIF(I$6:I$72,"취약"))</f>
       </c>
       <c r="J73" s="14"/>
@@ -58488,7 +58575,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -59994,31 +60081,31 @@
       <c r="B73" s="314" t="s">
         <v>179</v>
       </c>
-      <c r="C73" s="316" t="s">
+      <c r="C73" s="419" t="s">
         <v>255</v>
       </c>
       <c r="D73" s="317"/>
       <c r="E73" s="318"/>
-      <c r="F73" s="31">
+      <c r="F73" s="416">
         <f>IF(COUNTIF(F$6:F$72,"?*")=0,"",COUNTIF(F$6:F$72,"취약"))</f>
       </c>
       <c r="G73" s="86"/>
-      <c r="H73" s="31">
+      <c r="H73" s="416">
         <f>IF(COUNTIF(H$6:H$72,"?*")=0,"",COUNTIF(H$6:H$72,"취약"))</f>
       </c>
       <c r="I73" s="54"/>
-      <c r="J73" s="31">
+      <c r="J73" s="416">
         <f>IF(COUNTIF(J$6:J$72,"?*")=0,"",COUNTIF(J$6:J$72,"취약"))</f>
       </c>
       <c r="K73" s="54"/>
-      <c r="L73" s="31">
+      <c r="L73" s="416">
         <f>IF(COUNTIF(L$6:L$72,"?*")=0,"",COUNTIF(L$6:L$72,"취약"))</f>
       </c>
       <c r="M73" s="103"/>
     </row>
     <row r="74" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
       <c r="B74" s="271"/>
-      <c r="C74" s="301" t="s">
+      <c r="C74" s="420" t="s">
         <v>181</v>
       </c>
       <c r="D74" s="302"/>
@@ -60058,7 +60145,7 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
@@ -60067,8 +60154,8 @@
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="L3:L5"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
     <mergeCell ref="B6:B18"/>
     <mergeCell ref="B19:B38"/>
     <mergeCell ref="B39:B68"/>

--- a/infra_auto_diag/보고서_양식_Linux.xlsx
+++ b/infra_auto_diag/보고서_양식_Linux.xlsx
@@ -6915,12 +6915,9 @@
       </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
+      <font>
+        <color theme="1"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">

--- a/infra_auto_diag/보고서_양식_Linux.xlsx
+++ b/infra_auto_diag/보고서_양식_Linux.xlsx
@@ -4629,13 +4629,7 @@
         <color rgb="FFFFC000"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
     <dxf>
       <font>
         <i/>
@@ -5560,13 +5554,7 @@
         <color rgb="FFFFC000"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
     <dxf>
       <font>
         <i/>
@@ -6245,13 +6233,7 @@
         <color rgb="FFFFC000"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
     <dxf>
       <font>
         <i/>
@@ -6432,13 +6414,7 @@
         <color rgb="FF0070C0"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
     <dxf>
       <font>
         <i/>
@@ -6552,13 +6528,7 @@
         <color rgb="FF0070C0"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
     <dxf>
       <font>
         <i/>
